--- a/experiments/04_lora_finetuning/report/base_few_shot_vs_lora_zero_shot_1_epoch.xlsx
+++ b/experiments/04_lora_finetuning/report/base_few_shot_vs_lora_zero_shot_1_epoch.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,6 +26,12 @@
       <scheme val="minor"/>
     </font>
     <font/>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -36,20 +42,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF00B050"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -167,10 +173,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>

--- a/experiments/04_lora_finetuning/report/base_few_shot_vs_lora_zero_shot_1_epoch.xlsx
+++ b/experiments/04_lora_finetuning/report/base_few_shot_vs_lora_zero_shot_1_epoch.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,11 @@
     <font>
       <color rgb="00006100"/>
     </font>
+    <font>
+      <color rgb="009C6500"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +61,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -162,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -174,6 +183,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -672,24 +684,24 @@
       <c r="G3" s="6" t="n">
         <v>0.7631</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="8" t="n">
         <v>37.59</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="8" t="n">
         <v>66.76000000000001</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="J3" s="8" t="n">
         <v>51.72</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="K3" s="7" t="n">
         <v>0.8825</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="L3" s="8" t="n">
         <v>0.7812</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
+      <c r="A4" s="9" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
           <t>enes</t>
@@ -704,25 +716,25 @@
       <c r="E4" s="7" t="n">
         <v>82.95</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>0.9012</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0.7817</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="8" t="n">
         <v>55.53</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="8" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="7" t="n">
         <v>82.66</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>0.9074</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="L4" s="8" t="n">
         <v>0.8012</v>
       </c>
     </row>
@@ -739,19 +751,19 @@
       <c r="D5" s="6" t="n">
         <v>57.99</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>62.43</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>0.8879</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>0.6907</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="8" t="n">
         <v>35.96</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="8" t="n">
         <v>65.47</v>
       </c>
       <c r="J5" s="6" t="n">
@@ -760,7 +772,7 @@
       <c r="K5" s="7" t="n">
         <v>0.8904</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="L5" s="8" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -784,19 +796,19 @@
       <c r="E6" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>0.8941</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>0.7939000000000001</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="8" t="n">
         <v>42.67</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="8" t="n">
         <v>70.54000000000001</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="8" t="n">
         <v>57.3</v>
       </c>
       <c r="K6" s="7" t="n">
@@ -807,7 +819,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
           <t>enes</t>
@@ -822,19 +834,19 @@
       <c r="E7" s="6" t="n">
         <v>82.95</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>0.9004</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>0.7992</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="8" t="n">
         <v>59.93</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="8" t="n">
         <v>79.93000000000001</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="8" t="n">
         <v>83.81999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
@@ -857,19 +869,19 @@
       <c r="D8" s="6" t="n">
         <v>60.52</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>67.56999999999999</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>0.8815</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.6868</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>42.76</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="8" t="n">
         <v>69.83</v>
       </c>
       <c r="J8" s="7" t="n">
@@ -878,7 +890,7 @@
       <c r="K8" s="7" t="n">
         <v>0.8868</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="L8" s="8" t="n">
         <v>0.7043</v>
       </c>
     </row>
